--- a/review/abilities/workbooks/24_Class_Odd.xlsx
+++ b/review/abilities/workbooks/24_Class_Odd.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Level 1'!$A$4:$M$7</definedName>
@@ -25,11 +25,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Level 7'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'All Signatures'!$A$4:$M$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'All Signatures'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Power Watchlist'!$A$4:$J$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Power Watchlist'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -40,7 +38,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,14 +86,8 @@
       <color rgb="001F1F1F"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -115,11 +107,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4F7FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -149,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -175,15 +162,12 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -220,19 +204,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -612,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -758,7 +729,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>• Level 7: Apply ingenious force, escape with a partner, or turn pain into a response.</t>
+          <t>• Level 7: Borrow another’s competence, fill the field with spectral witnesses, or postpone a companion’s Last Words.</t>
         </is>
       </c>
     </row>
@@ -769,10 +740,10 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
+    <row r="21" ht="46" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Generalist and improviser. Signatures reframe tasks, distract, create alternative routes and grant unexpected movement. The class has no attribute minimums and treats every discipline as adjacent, so it is the natural home for unusual builds.</t>
+          <t>Generalist and improviser. Signatures reframe tasks, borrow expertise, create spectral distractions and temporary routes, and postpone a companion's Last Words. The class has no attribute minimums and treats every discipline as adjacent, so it is the natural home for unusual builds.</t>
         </is>
       </c>
     </row>
@@ -786,7 +757,7 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Maximum flexibility; strong skill scenes; Sideways Thinking and Change the Question give the class a clear problem-solving identity. One Last Remark is a great emotional capstone.</t>
+          <t>Maximum flexibility; strong skill scenes; Borrowed Tongue and A Door Where There Wasn’t give the class a clear problem-solving identity. Use Their Voice and The Unseen Procession control the field, and Not Quite Yet is an emotional capstone.</t>
         </is>
       </c>
     </row>
@@ -797,10 +768,10 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1">
+    <row r="27" ht="46" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Many effects are conditional or once per scene; the class can feel like a collection of tricks rather than a clear identity. Always a Way Around and Shoulder Through are Force-specific, so a non-Force Odd may ignore them. Strange but Effective has a copy error.</t>
+          <t>Many effects are conditional or once per scene; the class can feel like a collection of tricks rather than a clear identity. Pocket Sand and Foul Wind are its most direct offensive options, so a support-heavy build may need a deliberate damage plan. Borrowed Life and Not Quite Yet are high-impact once-per-scene/day effects to watch in play.</t>
         </is>
       </c>
     </row>
@@ -814,7 +785,7 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Clarify in the class guidance that Odd is a generalist and name two or three builds. Broaden the Force-specific signatures or accept them as support picks. Fix the missing push numerals in Strange but Effective.</t>
+          <t>Clarify in the class guidance that Odd is a generalist and name two or three builds. Show Borrowed Tongue and The Unseen Procession in an example of play. Keep the once-per-scene limits prominent on the cards.</t>
         </is>
       </c>
     </row>
@@ -855,7 +826,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Sideways Thinking; Useful Interruption; Always a Way Around</t>
+          <t>Borrowed Tongue; Use Their Voice; Pocket Sand</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
@@ -875,7 +846,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Unlikely Assistant; Change the Question; Wrong Place for That</t>
+          <t>Foul Wind; A Door Where There Wasn’t; Out of Body</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -895,7 +866,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Strange but Effective; An Unexpected Exit; One Last Remark</t>
+          <t>Borrowed Life; The Unseen Procession; Not Quite Yet</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
@@ -936,65 +907,43 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="66.5" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>F20</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Outcome lines read '2 progress, grapple reduction, or squares of push' and '3 progress, Grappled reduction, or squares of push'; the push numeral is missing in five lines across the two cards.</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Write the numeral every time: 'or 1 square of push', 'or 2 squares of push', etc. Check other multi-option outcome lines for the same pattern.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>How to use this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>• Level 1, Level 3 and Level 7 each show the three signatures available at that milestone.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>• Level 1, Level 3 and Level 7 each show the three signatures available at that milestone.</t>
+          <t>• All Signatures combines the nine rows for sorting and comparison.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>• All Signatures combines the nine rows for sorting and comparison.</t>
+          <t>• Balance Check shows the action economy and role coverage, then lists the power watchlist and design questions for this class.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>• Balance Check shows the action economy and role coverage, then lists the power watchlist and design questions for this class.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
+          <t>• The Decision column is a dropdown. Your notes is blank for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>• The Decision column is a dropdown. Your notes is blank for you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>• Stable ID is the Foundry/web contract. Record every field change on the Change Log sheet; the authoritative ledger is review/CHANGE_LEDGER.csv.</t>
         </is>
@@ -1020,6 +969,7 @@
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="A46:D46"/>
@@ -1029,7 +979,6 @@
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A14:D14"/>
@@ -1155,50 +1104,50 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="79" customHeight="1">
+    <row r="5" ht="54" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Always a Way Around</t>
+          <t>Borrowed Tongue</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>signature-odd-always-a-way-around</t>
+          <t>signature-odd-sideways-thinking</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Maneuver in combat, or one minute out of combat</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Self, after you resolve Force.</t>
+          <t>Self; one language you hear spoken.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Move up to 2 squares without provoking after your Force action. If you reduced your own Grappled rating to 0, you may stand without spending movement before taking this move. The card does not let you use Force without a Main Action or move while still Grappled.</t>
+          <t>A spirit that knows the language possesses you. You understand and speak that language for the scene. You do not read or write it.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Move up to 2 squares without provoking after your Force action. If you reduced your own Grappled rating to 0, you may stand without spending movement before taking this move. The card does not let you use Force without a Main Action or move while still Grappled.</t>
+          <t>A spirit that knows the language possesses you. You understand and speak that language for the scene. You do not read or write it.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Free 2-square move after Force; good for a Force-focused Odd and a clean expression of 'always another route'.</t>
+          <t>Borrowed Tongue: a spirit that knows a heard language possesses the Odd, granting understanding and speech for the scene. Strong social/exploration utility.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Narrow if the character never uses Force. Consider allowing a 1-square move after any Brawn action, or state in the class guidance that this is a Force-support pick.</t>
+          <t>Approved: Maneuver in combat or one minute out of combat; self; one language heard spoken; understand and speak it for the scene; no reading/writing; once per scene, one language at a time.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1217,47 +1166,48 @@
     <row r="6" ht="79" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Sideways Thinking</t>
+          <t>Pocket Sand</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-odd-sideways-thinking</t>
+          <t>signature-odd-always-a-way-around</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Reaction</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Self, before an ordinary noncombat task roll.</t>
+          <t>That enemy.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Describe a plausible approach based on reasoning. Use Reason for that roll and gain 1 Boon. You still need any specialist permission and suitable tools. This cannot replace an attribute printed on another learned card or make an impossible action possible.</t>
+          <t>Trigger: An enemy within 2 squares makes an attack or skill roll and can see you.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Describe a plausible approach based on reasoning. Use Reason for that roll and gain 1 Boon. You still need any specialist permission and suitable tools. This cannot replace an attribute printed on another learned card or make an impossible action possible.</t>
+          <t>Trigger: An enemy within 2 squares makes an attack or skill roll and can see you.
+Throw grit or debris into its face. The target takes 1 Bane to that roll. After the roll resolves, it gains Blinded 1 until the end of its next turn.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Once per scene, use Reason and gain 1 Boon on an ordinary noncombat roll; strong skill flexibility.</t>
+          <t>Pocket Sand: Reaction when an enemy within 2 makes an attack or skill roll; 1 Bane to that roll, then Blinded 1 until the end of its next turn. Petty, prepared and memorable.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Very broad; monitor. Clarify whether it can apply to a roll that already uses Reason (it replaces the attribute, so likely no double benefit) and what counts as 'ordinary'.</t>
+          <t>Approved: Reaction; enemy within 2 that can see you; 1 Bane to the triggering roll; after it resolves, Blinded 1 until the end of its next turn; once per scene.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1273,10 +1223,10 @@
       <c r="L6" s="8" t="inlineStr"/>
       <c r="M6" s="8" t="inlineStr"/>
     </row>
-    <row r="7" ht="91.5" customHeight="1">
+    <row r="7" ht="79" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Useful Interruption</t>
+          <t>Use Their Voice</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1291,32 +1241,32 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>One creature within 3 squares that can see or hear your distraction; one willing ally within 3 squares.</t>
+          <t>One enemy within 5 squares that can hear you; one willing ally within 5 squares that can see or hear you.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Describe a distraction the creature can perceive. The ally may move up to 2 squares without provoking from that creature. It also gains 1 Boon to its next roll against that creature before the start of your next turn. Other enemies can still react to the movement. This does not compel belief or grant Hidden.</t>
+          <t>The spirit calls out in the target’s own voice from a point you choose within 5 squares. The target turns toward the voice. The ally may move up to 2 squares without provoking and gains 1 Boon to its next attack against that target before the start of your next turn.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Describe a distraction the creature can perceive. The ally may move up to 2 squares without provoking from that creature. It also gains 1 Boon to its next roll against that creature before the start of your next turn. Other enemies can still react to the movement. This does not compel belief or grant Hidden.</t>
+          <t>The spirit calls out in the target’s own voice from a point you choose within 5 squares. The target turns toward the voice. The ally may move up to 2 squares without provoking and gains 1 Boon to its next attack against that target before the start of your next turn.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Distraction grants an ally a 2-square move and a Boon against that creature; strong setup.</t>
+          <t>Use Their Voice: a spirit only the Odd perceives calls out in the target’s own voice; an ally moves 2 and gains a Boon against the distracted target. Strong misdirection.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the ally's movement can provoke from other enemies (text says yes) and whether the Boon applies to attacks as well as skills.</t>
+          <t>Approved: Maneuver; enemy within 5 that can hear; ally within 5 that can see or hear the Odd; ally moves 2 without provoking and gains 1 Boon to next attack against the target; once per turn.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1349,15 +1299,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1481,10 +1428,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="91.5" customHeight="1">
+    <row r="5" ht="54" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Change the Question</t>
+          <t>A Door Where There Wasn’t</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -1494,37 +1441,37 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Main Action</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>One noncombat obstacle you and your companions can examine.</t>
+          <t>Self; one nonmagical barrier within reach.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Spend one minute examining the obstacle and describe an alternative approach. The DA identifies one workable alternative using available people, tools or features, if one exists, and states its risks. If none exists, learn the concrete missing resource or access that prevents it.</t>
+          <t>A door-sized opening appears in the barrier. Only you and your worn or carried gear can pass through it. The opening closes immediately after you pass through or at the end of your next turn.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Spend one minute examining the obstacle and describe an alternative approach. The DA identifies one workable alternative using available people, tools or features, if one exists, and states its risks. If none exists, learn the concrete missing resource or access that prevents it. You and one ally each gain 1 Boon to the next roll pursuing that alternative this scene. This grants no automatic success or specialist permission.</t>
+          <t>A door-sized opening appears in the barrier. Only you and your worn or carried gear can pass through it. The opening closes immediately after you pass through or at the end of your next turn.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>One-minute alternative-approach analysis; grants 2 Boons across you and an ally. Strong utility and a clear Odd fantasy.</t>
+          <t>A Door Where There Wasn’t: Maneuver to open a temporary door-sized passage in a nonmagical barrier. Only the Odd and carried gear can pass; it closes after passage or at the end of the next turn.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the alternative must be plausible to the DA and whether it can bypass a specialist requirement (text says no). A worked example would help.</t>
+          <t>Approved: Maneuver; nonmagical barrier within reach, max one square thick; only the Odd and worn/carried gear pass; once per scene; closes after passage or end of next turn.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1540,10 +1487,10 @@
       <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
     </row>
-    <row r="6" ht="66.5" customHeight="1">
+    <row r="6" ht="79" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Unlikely Assistant</t>
+          <t>Foul Wind</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -1553,37 +1500,37 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Fortitude</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>One ally within 3 squares that can understand your Aid.</t>
+          <t>Self; each willing ally within 5 squares; then each non-prone creature within 5 squares other than you.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Your Aid reaches that ally and grants 2 Boons instead of 1 to the declared task’s next roll. Describe how your unusual method helps. It grants no missing specialist permission, extra crafting attempt or additional contribution to a group check.</t>
+          <t>Each willing ally within 5 squares may immediately fall prone. Make one Fortitude roll. Each non-prone creature within 5 squares other than you takes 1 poison damage on a Weak result, 2 poison damage on a Standard result, or 4 poison damage on a Strong result.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Your Aid reaches that ally and grants 2 Boons instead of 1 to the declared task’s next roll. Describe how your unusual method helps. It grants no missing specialist permission, extra crafting attempt or additional contribution to a group check.</t>
+          <t>Each willing ally within 5 squares may immediately fall prone. Make one Fortitude roll. Each non-prone creature within 5 squares other than you takes 1 poison damage on a Weak result, 2 poison damage on a Standard result, or 4 poison damage on a Strong result.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Aid grants 2 Boons instead of 1; simple and strong.</t>
+          <t>Foul Wind: Main Action Fortitude area poison. Allies may drop prone to avoid it; non-prone creatures within 5 take 1/2/4 poison. Strong crowd control with friendly-fire setup.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Compare to Leader Follow My Signal (two allies, 1 Boon each). Clarify whether the 2 Boons must apply to one roll or can be split.</t>
+          <t>Approved: Main Action, Fortitude, willing allies within 5 may fall prone, non-prone creatures within 5 other than the Odd take 1/2/4 poison, once per turn.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1599,10 +1546,10 @@
       <c r="L6" s="8" t="inlineStr"/>
       <c r="M6" s="8" t="inlineStr"/>
     </row>
-    <row r="7" ht="66.5" customHeight="1">
+    <row r="7" ht="254" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Wrong Place for That</t>
+          <t>Out of Body</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1612,37 +1559,42 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Reaction</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Self and one adjacent willing ally, after an attack against either of you resolves.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>You and that ally may each move up to 2 squares without provoking. Choose the order and legal free endpoints. Each must still be able to move. The triggering attack has already resolved; this provides no retroactive protection.</t>
+          <t>Your body falls prone and cannot act, move or take Reactions. It has 3 defense Banes. Your spirit appears in your square or an adjacent free square.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>You and that ally may each move up to 2 squares without provoking. Choose the order and legal free endpoints. Each must still be able to move. The triggering attack has already resolved; this provides no retroactive protection.</t>
+          <t>Your body falls prone and cannot act, move or take Reactions. It has 3 defense Banes. Your spirit appears in your square or an adjacent free square.
+The spirit has Speed 5, can speak, can pass through nonmagical solid objects and creatures, and is immune to mundane attacks. It cannot attack, cast spells, use equipment or physically interact with objects. Its movement does not provoke opportunity attacks. Magical attacks can target it; resolve them against your normal defenses, and damage to the spirit is damage to your body. If your body drops to 0 HP, the projection ends.
+At the end of your turn, choose one:
+• Snap Back: Your spirit returns to your body.
+• Manifest: Your body appears in the spirit’s square or the nearest free square that is not separated from your body by a solid barrier, prone. The projection ends.
+If no legal Manifest square exists, you can only Snap Back.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Reaction move 2 for self and an ally after an attack; strong repositioning and a good 'escape the blast' moment.</t>
+          <t>Out of Body: Main Action projection. Body is prone with 3 defense Banes; spirit has Speed 5, passes through nonmagical solids, immune to mundane attacks, and can Snap Back or Manifest the body to a legal free square at turn end. Strong scouting and short reposition.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether either can move if Prone or immobilized and whether the movement can leave melee (yes, if able).</t>
+          <t>Approved: Main Action; body prone, no actions/movement/Reactions, 3 defense Banes; spirit Speed 5, speaks, passes through nonmagical solids and creatures, immune to mundane attacks, magic damages body; Snap Back or Manifest to a free square not separated by a solid barrier; no once-per-scene limit.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1675,15 +1627,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1807,50 +1756,50 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="79" customHeight="1">
+    <row r="5" ht="66.5" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>An Unexpected Exit</t>
+          <t>Borrowed Life</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>signature-odd-an-unexpected-exit</t>
+          <t>signature-odd-strange-but-effective</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Self and optionally one adjacent willing ally.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Move up to your Speed without provoking. The ally may follow along a legal route up to the same distance, spending no action, and must end in a separate free square adjacent to you. Both must be able to move; this does not cross standing occupied squares, barriers or otherwise impassable terrain.</t>
+          <t>Once per scene, invite a spirit into your body. Choose one skill, tool or weapon. For the scene, you gain 3 Boons to rolls using that expertise. The spirit speaks through you and colors your mannerisms, but you remain in control.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Move up to your Speed without provoking. The ally may follow along a legal route up to the same distance, spending no action, and must end in a separate free square adjacent to you. Both must be able to move; this does not cross standing occupied squares, barriers or otherwise impassable terrain.</t>
+          <t>Once per scene, invite a spirit into your body. Choose one skill, tool or weapon. For the scene, you gain 3 Boons to rolls using that expertise. The spirit speaks through you and colors your mannerisms, but you remain in control.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Move your Speed and bring an ally; excellent escape and a strong expression of the class.</t>
+          <t>Invite a spirit into your body to borrow expertise: gain 3 Boons on one skill, tool, or weapon for the scene. The spirit speaks through you and colors your mannerisms, but you remain in control.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the ally must stay adjacent throughout or only at the end (text says end adjacent), and whether either can move if Grappled.</t>
+          <t>Approved: Main Action, no roll, self. Once per scene, choose one skill, tool, or weapon; gain 3 Boons to rolls using that expertise for the scene. The spirit speaks through you and colors your mannerisms; you remain in control.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1866,10 +1815,10 @@
       <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
     </row>
-    <row r="6" ht="154" customHeight="1">
+    <row r="6" ht="79" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>One Last Remark</t>
+          <t>Not Quite Yet</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -1884,34 +1833,32 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>One willing ally within 4 squares that can hear you, after it takes damage; alternatively, when you hear an ally’s Last Words within 4 squares.</t>
+          <t>One ally within 5 squares that would enter Last Words.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>After damage resolves, the chosen ally may move up to 3 squares without provoking or make one free Basic Melee attack against an adjacent enemy. It must be able to take the chosen action.</t>
+          <t>The ally does not enter Last Words yet. It remains at 0 HP with at least three death marks until the end of its next turn and makes no further death rolls during the delay. If it is stabilized or healed above 0 before then, it avoids Last Words.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>After damage resolves, the chosen ally may move up to 3 squares without provoking or make one free Basic Melee attack against an adjacent enemy. It must be able to take the chosen action.
-If triggered by Last Words instead, choose up to two other willing allies within 4 squares that can hear you; each chooses one of those benefits. The dying speaker gains no action, and its death is neither delayed nor reversed.
-Basic Melee uses each attacker’s Brawn, weapon and normal outcomes. Damage from a free attack cannot trigger a free attack through this card; no further free attacks arise from these attacks.</t>
+          <t>The ally does not enter Last Words yet. It remains at 0 HP with at least three death marks until the end of its next turn and makes no further death rolls during the delay. If it is stabilized or healed above 0 before then, it avoids Last Words. At the end of its next turn, if it still has three death marks, Last Words begin.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Reaction ally move 3 or free attack; on Last Words, two allies benefit. Strong, thematic and emotionally resonant.</t>
+          <t>Reaction that postpones a companion's Last Words by one turn, giving the party a final chance to save them without negating the death clock.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify the trigger order and whether the ally can choose a benefit if it is Dying; text says it must be able. Add a Last Words example.</t>
+          <t>Approved: Reaction, once per day per character. When a companion within 5 squares would begin Last Words, they delay onset until the end of their next turn. They can act and be targeted normally but make no death rolls; if they still have 3 death marks then, Last Words begin.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1927,15 +1874,15 @@
       <c r="L6" s="8" t="inlineStr"/>
       <c r="M6" s="8" t="inlineStr"/>
     </row>
-    <row r="7" ht="141.5" customHeight="1">
+    <row r="7" ht="66.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Strange but Effective</t>
+          <t>The Unseen Procession</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>signature-odd-strange-but-effective</t>
+          <t>signature-odd-an-unexpected-exit</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1945,46 +1892,42 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Guile</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>One adjacent obstacle or creature, or your own Grappled condition.</t>
+          <t>You and each ally within 5 squares; each enemy within 5 squares.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Choose Force’s intended result before rolling: obstacle progress, reducing your Grappled rating, or pushing a creature. Describe a plausible means of exerting force.</t>
+          <t>Once per scene, spectral figures fill the area. You and each ally gain 1 Boon to your next defense and may move 1 square without provoking. Each enemy gains 1 Bane to its next attack.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Choose Force’s intended result before rolling: obstacle progress, reducing your Grappled rating, or pushing a creature. Describe a plausible means of exerting force.
-• Weak: 2 progress, Grappled reduction, or squares of push.
-• Standard: 3 progress, Grappled reduction, or squares of push.
-• Strong: 4 progress, Grappled reduction, or squares of push.
-Afterward you may move up to 2 squares without provoking if able. Grappled 3 leaves no Main Action to spend; this cannot release a fully restrained user.</t>
+          <t>Once per scene, spectral figures fill the area. You and each ally gain 1 Boon to your next defense and may move 1 square without provoking. Each enemy gains 1 Bane to its next attack.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Use Guile for Force with better outcomes and a 2-square move; strong signature and a clear 'unexpected solution' identity.</t>
+          <t>Fill the area with spectral witnesses: allies gain a defensive boon and a free step; enemies take a bane on their next attack. Strong, thematic control.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Fix the missing push numerals in the outcome lines (2/3/4). Clarify whether the move can occur if the Force attempt fails.</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Approved: Main Action, no roll. You and each ally within 5 gain 1 Boon to the next defense and may move 1 square without provoking; each enemy within 5 gains 1 Bane to its next attack. Lasts until end of round; once per scene.</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Missing numeral</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr"/>
@@ -2007,15 +1950,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2139,7 +2079,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="79" customHeight="1">
+    <row r="5" ht="54" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>1</t>
@@ -2147,42 +2087,42 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Always a Way Around</t>
+          <t>Borrowed Tongue</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>signature-odd-always-a-way-around</t>
+          <t>signature-odd-sideways-thinking</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Maneuver in combat, or one minute out of combat</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Self, after you resolve Force.</t>
+          <t>Self; one language you hear spoken.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Move up to 2 squares without provoking after your Force action. If you reduced your own Grappled rating to 0, you may stand without spending movement before taking this move. The card does not let you use Force without a Main Action or move while still Grappled.</t>
+          <t>A spirit that knows the language possesses you. You understand and speak that language for the scene. You do not read or write it.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Free 2-square move after Force; good for a Force-focused Odd and a clean expression of 'always another route'.</t>
+          <t>Borrowed Tongue: a spirit that knows a heard language possesses the Odd, granting understanding and speech for the scene. Strong social/exploration utility.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Narrow if the character never uses Force. Consider allowing a 1-square move after any Brawn action, or state in the class guidance that this is a Force-support pick.</t>
+          <t>Approved: Maneuver in combat or one minute out of combat; self; one language heard spoken; understand and speak it for the scene; no reading/writing; once per scene, one language at a time.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -2198,7 +2138,7 @@
       <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
     </row>
-    <row r="6" ht="79" customHeight="1">
+    <row r="6" ht="54" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>1</t>
@@ -2206,42 +2146,42 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sideways Thinking</t>
+          <t>Pocket Sand</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>signature-odd-sideways-thinking</t>
+          <t>signature-odd-always-a-way-around</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Reaction</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Self, before an ordinary noncombat task roll.</t>
+          <t>That enemy.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Describe a plausible approach based on reasoning. Use Reason for that roll and gain 1 Boon. You still need any specialist permission and suitable tools. This cannot replace an attribute printed on another learned card or make an impossible action possible.</t>
+          <t>Trigger: An enemy within 2 squares makes an attack or skill roll and can see you.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Once per scene, use Reason and gain 1 Boon on an ordinary noncombat roll; strong skill flexibility.</t>
+          <t>Pocket Sand: Reaction when an enemy within 2 makes an attack or skill roll; 1 Bane to that roll, then Blinded 1 until the end of its next turn. Petty, prepared and memorable.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Very broad; monitor. Clarify whether it can apply to a roll that already uses Reason (it replaces the attribute, so likely no double benefit) and what counts as 'ordinary'.</t>
+          <t>Approved: Reaction; enemy within 2 that can see you; 1 Bane to the triggering roll; after it resolves, Blinded 1 until the end of its next turn; once per scene.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -2257,7 +2197,7 @@
       <c r="L6" s="8" t="inlineStr"/>
       <c r="M6" s="8" t="inlineStr"/>
     </row>
-    <row r="7" ht="91.5" customHeight="1">
+    <row r="7" ht="79" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>1</t>
@@ -2265,7 +2205,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Useful Interruption</t>
+          <t>Use Their Voice</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -2280,27 +2220,27 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>One creature within 3 squares that can see or hear your distraction; one willing ally within 3 squares.</t>
+          <t>One enemy within 5 squares that can hear you; one willing ally within 5 squares that can see or hear you.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Describe a distraction the creature can perceive. The ally may move up to 2 squares without provoking from that creature. It also gains 1 Boon to its next roll against that creature before the start of your next turn. Other enemies can still react to the movement. This does not compel belief or grant Hidden.</t>
+          <t>The spirit calls out in the target’s own voice from a point you choose within 5 squares. The target turns toward the voice. The ally may move up to 2 squares without provoking and gains 1 Boon to its next attack against that target before the start of your next turn.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Distraction grants an ally a 2-square move and a Boon against that creature; strong setup.</t>
+          <t>Use Their Voice: a spirit only the Odd perceives calls out in the target’s own voice; an ally moves 2 and gains a Boon against the distracted target. Strong misdirection.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the ally's movement can provoke from other enemies (text says yes) and whether the Boon applies to attacks as well as skills.</t>
+          <t>Approved: Maneuver; enemy within 5 that can hear; ally within 5 that can see or hear the Odd; ally moves 2 without provoking and gains 1 Boon to next attack against the target; once per turn.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -2316,7 +2256,7 @@
       <c r="L7" s="7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
     </row>
-    <row r="8" ht="79" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>3</t>
@@ -2324,7 +2264,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Change the Question</t>
+          <t>A Door Where There Wasn’t</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -2334,32 +2274,32 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Main Action</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>One noncombat obstacle you and your companions can examine.</t>
+          <t>Self; one nonmagical barrier within reach.</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Spend one minute examining the obstacle and describe an alternative approach. The DA identifies one workable alternative using available people, tools or features, if one exists, and states its risks. If none exists, learn the concrete missing resource or access that prevents it.</t>
+          <t>A door-sized opening appears in the barrier. Only you and your worn or carried gear can pass through it. The opening closes immediately after you pass through or at the end of your next turn.</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>One-minute alternative-approach analysis; grants 2 Boons across you and an ally. Strong utility and a clear Odd fantasy.</t>
+          <t>A Door Where There Wasn’t: Maneuver to open a temporary door-sized passage in a nonmagical barrier. Only the Odd and carried gear can pass; it closes after passage or at the end of the next turn.</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether the alternative must be plausible to the DA and whether it can bypass a specialist requirement (text says no). A worked example would help.</t>
+          <t>Approved: Maneuver; nonmagical barrier within reach, max one square thick; only the Odd and worn/carried gear pass; once per scene; closes after passage or end of next turn.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -2375,7 +2315,7 @@
       <c r="L8" s="8" t="inlineStr"/>
       <c r="M8" s="8" t="inlineStr"/>
     </row>
-    <row r="9" ht="66.5" customHeight="1">
+    <row r="9" ht="79" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>3</t>
@@ -2383,7 +2323,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Unlikely Assistant</t>
+          <t>Foul Wind</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -2393,32 +2333,32 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Fortitude</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>One ally within 3 squares that can understand your Aid.</t>
+          <t>Self; each willing ally within 5 squares; then each non-prone creature within 5 squares other than you.</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Your Aid reaches that ally and grants 2 Boons instead of 1 to the declared task’s next roll. Describe how your unusual method helps. It grants no missing specialist permission, extra crafting attempt or additional contribution to a group check.</t>
+          <t>Each willing ally within 5 squares may immediately fall prone. Make one Fortitude roll. Each non-prone creature within 5 squares other than you takes 1 poison damage on a Weak result, 2 poison damage on a Standard result, or 4 poison damage on a Strong result.</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Aid grants 2 Boons instead of 1; simple and strong.</t>
+          <t>Foul Wind: Main Action Fortitude area poison. Allies may drop prone to avoid it; non-prone creatures within 5 take 1/2/4 poison. Strong crowd control with friendly-fire setup.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Compare to Leader Follow My Signal (two allies, 1 Boon each). Clarify whether the 2 Boons must apply to one roll or can be split.</t>
+          <t>Approved: Main Action, Fortitude, willing allies within 5 may fall prone, non-prone creatures within 5 other than the Odd take 1/2/4 poison, once per turn.</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -2434,7 +2374,7 @@
       <c r="L9" s="7" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
     </row>
-    <row r="10" ht="66.5" customHeight="1">
+    <row r="10" ht="91.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>3</t>
@@ -2442,7 +2382,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Wrong Place for That</t>
+          <t>Out of Body</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -2452,32 +2392,32 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Reaction</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Self and one adjacent willing ally, after an attack against either of you resolves.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>You and that ally may each move up to 2 squares without provoking. Choose the order and legal free endpoints. Each must still be able to move. The triggering attack has already resolved; this provides no retroactive protection.</t>
+          <t>Your body falls prone and cannot act, move or take Reactions. It has 3 defense Banes. Your spirit appears in your square or an adjacent free square.</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Reaction move 2 for self and an ally after an attack; strong repositioning and a good 'escape the blast' moment.</t>
+          <t>Out of Body: Main Action projection. Body is prone with 3 defense Banes; spirit has Speed 5, passes through nonmagical solids, immune to mundane attacks, and can Snap Back or Manifest the body to a legal free square at turn end. Strong scouting and short reposition.</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether either can move if Prone or immobilized and whether the movement can leave melee (yes, if able).</t>
+          <t>Approved: Main Action; body prone, no actions/movement/Reactions, 3 defense Banes; spirit Speed 5, speaks, passes through nonmagical solids and creatures, immune to mundane attacks, magic damages body; Snap Back or Manifest to a free square not separated by a solid barrier; no once-per-scene limit.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -2493,7 +2433,7 @@
       <c r="L10" s="8" t="inlineStr"/>
       <c r="M10" s="8" t="inlineStr"/>
     </row>
-    <row r="11" ht="79" customHeight="1">
+    <row r="11" ht="66.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>7</t>
@@ -2501,42 +2441,42 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>An Unexpected Exit</t>
+          <t>Borrowed Life</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>signature-odd-an-unexpected-exit</t>
+          <t>signature-odd-strange-but-effective</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Self and optionally one adjacent willing ally.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Move up to your Speed without provoking. The ally may follow along a legal route up to the same distance, spending no action, and must end in a separate free square adjacent to you. Both must be able to move; this does not cross standing occupied squares, barriers or otherwise impassable terrain.</t>
+          <t>Once per scene, invite a spirit into your body. Choose one skill, tool or weapon. For the scene, you gain 3 Boons to rolls using that expertise. The spirit speaks through you and colors your mannerisms, but you remain in control.</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Move your Speed and bring an ally; excellent escape and a strong expression of the class.</t>
+          <t>Invite a spirit into your body to borrow expertise: gain 3 Boons on one skill, tool, or weapon for the scene. The spirit speaks through you and colors your mannerisms, but you remain in control.</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the ally must stay adjacent throughout or only at the end (text says end adjacent), and whether either can move if Grappled.</t>
+          <t>Approved: Main Action, no roll, self. Once per scene, choose one skill, tool, or weapon; gain 3 Boons to rolls using that expertise for the scene. The spirit speaks through you and colors your mannerisms; you remain in control.</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -2560,7 +2500,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>One Last Remark</t>
+          <t>Not Quite Yet</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2575,27 +2515,27 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>One willing ally within 4 squares that can hear you, after it takes damage; alternatively, when you hear an ally’s Last Words within 4 squares.</t>
+          <t>One ally within 5 squares that would enter Last Words.</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>After damage resolves, the chosen ally may move up to 3 squares without provoking or make one free Basic Melee attack against an adjacent enemy. It must be able to take the chosen action.</t>
+          <t>The ally does not enter Last Words yet. It remains at 0 HP with at least three death marks until the end of its next turn and makes no further death rolls during the delay. If it is stabilized or healed above 0 before then, it avoids Last Words.</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Reaction ally move 3 or free attack; on Last Words, two allies benefit. Strong, thematic and emotionally resonant.</t>
+          <t>Reaction that postpones a companion's Last Words by one turn, giving the party a final chance to save them without negating the death clock.</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Clarify the trigger order and whether the ally can choose a benefit if it is Dying; text says it must be able. Add a Last Words example.</t>
+          <t>Approved: Reaction, once per day per character. When a companion within 5 squares would begin Last Words, they delay onset until the end of their next turn. They can act and be targeted normally but make no death rolls; if they still have 3 death marks then, Last Words begin.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -2611,7 +2551,7 @@
       <c r="L12" s="8" t="inlineStr"/>
       <c r="M12" s="8" t="inlineStr"/>
     </row>
-    <row r="13" ht="54" customHeight="1">
+    <row r="13" ht="66.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>7</t>
@@ -2619,12 +2559,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Strange but Effective</t>
+          <t>The Unseen Procession</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>signature-odd-strange-but-effective</t>
+          <t>signature-odd-an-unexpected-exit</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2634,37 +2574,37 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Guile</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>One adjacent obstacle or creature, or your own Grappled condition.</t>
+          <t>You and each ally within 5 squares; each enemy within 5 squares.</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Choose Force’s intended result before rolling: obstacle progress, reducing your Grappled rating, or pushing a creature. Describe a plausible means of exerting force.</t>
+          <t>Once per scene, spectral figures fill the area. You and each ally gain 1 Boon to your next defense and may move 1 square without provoking. Each enemy gains 1 Bane to its next attack.</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Use Guile for Force with better outcomes and a 2-square move; strong signature and a clear 'unexpected solution' identity.</t>
+          <t>Fill the area with spectral witnesses: allies gain a defensive boon and a free step; enemies take a bane on their next attack. Strong, thematic control.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Fix the missing push numerals in the outcome lines (2/3/4). Clarify whether the move can occur if the Force attempt fails.</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Approved: Main Action, no roll. You and each ally within 5 gain 1 Boon to the next defense and may move 1 square without provoking; each enemy within 5 gains 1 Bane to its next attack. Lasts until end of round; once per scene.</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Missing numeral</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr"/>
@@ -2687,15 +2627,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2809,13 +2746,13 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="D6" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
@@ -2842,16 +2779,16 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="D7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="E7" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>0</v>
@@ -2878,13 +2815,13 @@
         <v>0</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>0</v>
@@ -2968,22 +2905,22 @@
         <v>0</v>
       </c>
       <c r="D12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="7" t="n">
         <v>0</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
@@ -2993,16 +2930,16 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>0</v>
@@ -3014,7 +2951,7 @@
         <v>2</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1">
@@ -3024,7 +2961,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>0</v>
@@ -3033,19 +2970,19 @@
         <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -3055,17 +2992,17 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
+    <row r="17" ht="46" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>• Many effects are conditional or once per scene; the class can feel like a collection of tricks rather than a clear identity. Always a Way Around and Shoulder Through are Force-specific, so a non-Force Odd may ignore them. Strange but Effective has a copy error.</t>
+          <t>• Many effects are conditional or once per scene; the class can feel like a collection of tricks rather than a clear identity. Pocket Sand and Foul Wind are its most direct offensive options, so a support-heavy build may need a deliberate damage plan. Borrowed Life and Not Quite Yet are high-impact once-per-scene/day effects to watch in play.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>• Clarify in the class guidance that Odd is a generalist and name two or three builds. Broaden the Force-specific signatures or accept them as support picks. Fix the missing push numerals in Strange but Effective.</t>
+          <t>• Clarify in the class guidance that Odd is a generalist and name two or three builds. Show Borrowed Tongue and The Unseen Procession in an example of play. Keep the once-per-scene limits prominent on the cards.</t>
         </is>
       </c>
     </row>
@@ -3202,74 +3139,19 @@
       </c>
       <c r="J4" s="6" t="inlineStr"/>
     </row>
-    <row r="5" ht="29" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Strange but Effective</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>signature-odd-strange-but-effective</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Missing numeral</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Outcome lines say 'or squares of push' without a number.</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Write 2/3/4 squares of push.</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>No row-level flags for this class. Use the design questions on Balance Check.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J5"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>H5="Keep"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>H5="Revise"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>H5="Cut"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>H5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
-      <formula>H5="Unsure"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="H5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
-    </dataValidation>
-  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3291,7 +3173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3306,12 +3188,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="10" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="9" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3392,30 +3273,25 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3439,7 +3315,6 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr"/>
@@ -3459,7 +3334,6 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
@@ -3479,7 +3353,6 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
@@ -3499,7 +3372,6 @@
       <c r="O8" s="8" t="inlineStr"/>
       <c r="P8" s="8" t="inlineStr"/>
       <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr"/>
@@ -3519,7 +3391,6 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr"/>
@@ -3539,7 +3410,6 @@
       <c r="O10" s="8" t="inlineStr"/>
       <c r="P10" s="8" t="inlineStr"/>
       <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr"/>
@@ -3559,7 +3429,6 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr"/>
@@ -3579,7 +3448,6 @@
       <c r="O12" s="8" t="inlineStr"/>
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr"/>
@@ -3599,7 +3467,6 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr"/>
@@ -3619,7 +3486,6 @@
       <c r="O14" s="8" t="inlineStr"/>
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr"/>
@@ -3639,7 +3505,6 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr"/>
@@ -3659,23 +3524,19 @@
       <c r="O16" s="8" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr"/>
       <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>

--- a/review/abilities/workbooks/24_Class_Odd.xlsx
+++ b/review/abilities/workbooks/24_Class_Odd.xlsx
@@ -952,8 +952,8 @@
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="A20:D20"/>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>The ally does not enter Last Words yet. It remains at 0 HP with at least three death marks until the end of its next turn and makes no further death rolls during the delay. If it is stabilized or healed above 0 before then, it avoids Last Words.</t>
+          <t>The ally does not enter Last Words yet. It remains at 0 HP with at least three death marks until the beginning of its next turn and makes no further death rolls during the delay. If it is stabilized or healed above 0 before then, it avoids Last Words.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>The ally does not enter Last Words yet. It remains at 0 HP with at least three death marks until the end of its next turn and makes no further death rolls during the delay. If it is stabilized or healed above 0 before then, it avoids Last Words. At the end of its next turn, if it still has three death marks, Last Words begin.</t>
+          <t>The ally does not enter Last Words yet. It remains at 0 HP with at least three death marks until the beginning of its next turn and makes no further death rolls during the delay. If it is stabilized or healed above 0 before then, it avoids Last Words. At the beginning of its next turn, if it still has three death marks, Last Words begin.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -1871,8 +1871,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27. Delay ends at the beginning of the ally's next turn.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="66.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -2525,7 +2533,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>The ally does not enter Last Words yet. It remains at 0 HP with at least three death marks until the end of its next turn and makes no further death rolls during the delay. If it is stabilized or healed above 0 before then, it avoids Last Words.</t>
+          <t>The ally does not enter Last Words yet. It remains at 0 HP with at least three death marks until the beginning of its next turn and makes no further death rolls during the delay. If it is stabilized or healed above 0 before then, it avoids Last Words.</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -2535,7 +2543,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Approved: Reaction, once per day per character. When a companion within 5 squares would begin Last Words, they delay onset until the end of their next turn. They can act and be targeted normally but make no death rolls; if they still have 3 death marks then, Last Words begin.</t>
+          <t>Approved: Reaction, once per day per character. When a companion within 5 squares would begin Last Words, they delay onset until the beginning of their next turn. They can act and be targeted normally but make no death rolls; if they still have 3 death marks then, Last Words begin.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -2548,8 +2556,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L12" s="8" t="inlineStr"/>
-      <c r="M12" s="8" t="inlineStr"/>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27. Delay ends at the beginning of the ally's next turn.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="66.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -3173,7 +3189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3298,232 +3314,5897 @@
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr"/>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
-      <c r="K5" s="7" t="inlineStr"/>
-      <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>CHG-ODD-001</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>signature-odd-unlikely-assistant</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Foul Wind</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-unlikely-assistant.md</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Unlikely Assistant</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Foul Wind</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>The ability is now an absurd area attack.</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O5" s="7" t="inlineStr"/>
-      <c r="P5" s="7" t="inlineStr"/>
-      <c r="Q5" s="7" t="inlineStr"/>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="8" t="inlineStr"/>
-      <c r="B6" s="8" t="inlineStr"/>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>CHG-ODD-002</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>signature-odd-unlikely-assistant</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Foul Wind</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-unlikely-assistant.md</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>You wedge a boot where a tool should go, offer an unexpected comparison and somehow make the work easier.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>You drop low, spin, and let out a belch that smells like a grave. Your allies know what is coming and hit the ground.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Align the narrative with the belch.</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="7" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>CHG-ODD-003</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>signature-odd-unlikely-assistant</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Foul Wind</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-unlikely-assistant.md</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>The ability is now an active attack.</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O7" s="7" t="inlineStr"/>
-      <c r="P7" s="7" t="inlineStr"/>
-      <c r="Q7" s="7" t="inlineStr"/>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="8" t="inlineStr"/>
-      <c r="B8" s="8" t="inlineStr"/>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr"/>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>CHG-ODD-004</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>signature-odd-unlikely-assistant</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Foul Wind</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-unlikely-assistant.md</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>None (no roll)</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Fortitude</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>The belch is a Fortitude effect.</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O8" s="8" t="inlineStr"/>
-      <c r="P8" s="8" t="inlineStr"/>
-      <c r="Q8" s="8" t="inlineStr"/>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>Original metadata used an em dash; the new field uses the rules term.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>CHG-ODD-005</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>signature-odd-unlikely-assistant</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Foul Wind</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-unlikely-assistant.md</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>One ally within 3 squares that can understand your Aid.</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Self; each willing ally within 5 squares; then each non-prone creature within 5 squares other than you.</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>The ability now affects allies and non-prone creatures in range.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O9" s="7" t="inlineStr"/>
-      <c r="P9" s="7" t="inlineStr"/>
-      <c r="Q9" s="7" t="inlineStr"/>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="8" t="inlineStr"/>
-      <c r="B10" s="8" t="inlineStr"/>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr"/>
-      <c r="J10" s="8" t="inlineStr"/>
-      <c r="K10" s="8" t="inlineStr"/>
-      <c r="L10" s="8" t="inlineStr"/>
-      <c r="M10" s="8" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>CHG-ODD-006</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>signature-odd-unlikely-assistant</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Foul Wind</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-unlikely-assistant.md</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Your Aid reaches that ally and grants 2 Boons instead of 1 to the declared task’s next roll. Describe how your unusual method helps. It grants no missing specialist permission, extra crafting attempt or additional contribution to a group check.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Each willing ally within 5 squares may immediately fall prone. Make one Fortitude roll. Each non-prone creature within 5 squares other than you takes 1 poison damage on a Weak result, 2 poison damage on a Standard result, or 4 poison damage on a Strong result.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Bruce replaced the Aid upgrade with friendly-fire area poison.</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O10" s="8" t="inlineStr"/>
-      <c r="P10" s="8" t="inlineStr"/>
-      <c r="Q10" s="8" t="inlineStr"/>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="7" t="inlineStr"/>
-      <c r="B11" s="7" t="inlineStr"/>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr"/>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
-      <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>CHG-ODD-007</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>signature-odd-unlikely-assistant</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Foul Wind</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-unlikely-assistant.md</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Until the aided roll or the start of your next turn.</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Immediate.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>The belch resolves immediately.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O11" s="7" t="inlineStr"/>
-      <c r="P11" s="7" t="inlineStr"/>
-      <c r="Q11" s="7" t="inlineStr"/>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="8" t="inlineStr"/>
-      <c r="B12" s="8" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="8" t="inlineStr"/>
-      <c r="M12" s="8" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>CHG-ODD-008</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>signature-odd-unlikely-assistant</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Foul Wind</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-unlikely-assistant.md</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Normal Aid action and group-check restrictions apply.</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Once on your turn.</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>The area attack is limited to once per turn.</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O12" s="8" t="inlineStr"/>
-      <c r="P12" s="8" t="inlineStr"/>
-      <c r="Q12" s="8" t="inlineStr"/>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="7" t="inlineStr"/>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="7" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>CHG-ODD-009</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>signature-odd-unlikely-assistant</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Foul Wind</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-unlikely-assistant.md</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Skill / Utility</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Control</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>The ability is now an area attack.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O13" s="7" t="inlineStr"/>
-      <c r="P13" s="7" t="inlineStr"/>
-      <c r="Q13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="8" t="inlineStr"/>
-      <c r="B14" s="8" t="inlineStr"/>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="inlineStr"/>
-      <c r="J14" s="8" t="inlineStr"/>
-      <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="8" t="inlineStr"/>
-      <c r="M14" s="8" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>CHG-ODD-010</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>signature-odd-wrong-place-for-that</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Out of Body</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-wrong-place-for-that.md</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Wrong Place for That</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Out of Body</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>The ability is now spirit projection.</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O14" s="8" t="inlineStr"/>
-      <c r="P14" s="8" t="inlineStr"/>
-      <c r="Q14" s="8" t="inlineStr"/>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="7" t="inlineStr"/>
-      <c r="B15" s="7" t="inlineStr"/>
-      <c r="C15" s="7" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr"/>
-      <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>CHG-ODD-011</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>signature-odd-wrong-place-for-that</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Out of Body</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-wrong-place-for-that.md</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>You catch a companion by the sleeve and stumble away together, leaving the next blow aimed at suddenly empty ground.</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>You step out of yourself, leaving your body slumped and prone while your spirit moves free.</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Align the narrative with projection.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O15" s="7" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr"/>
-      <c r="Q15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="8" t="inlineStr"/>
-      <c r="B16" s="8" t="inlineStr"/>
-      <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="8" t="inlineStr"/>
-      <c r="J16" s="8" t="inlineStr"/>
-      <c r="K16" s="8" t="inlineStr"/>
-      <c r="L16" s="8" t="inlineStr"/>
-      <c r="M16" s="8" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>CHG-ODD-012</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>signature-odd-wrong-place-for-that</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Out of Body</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-wrong-place-for-that.md</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Reaction</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Projection is now an active Main Action.</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O16" s="8" t="inlineStr"/>
-      <c r="P16" s="8" t="inlineStr"/>
-      <c r="Q16" s="8" t="inlineStr"/>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CHG-ODD-013</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>signature-odd-wrong-place-for-that</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Out of Body</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-wrong-place-for-that.md</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Self and one adjacent willing ally, after an attack against either of you resolves.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Self.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>The projection affects only the Odd.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CHG-ODD-014</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>signature-odd-wrong-place-for-that</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Out of Body</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-wrong-place-for-that.md</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>You and that ally may each move up to 2 squares without provoking. Choose the order and legal free endpoints. Each must still be able to move. The triggering attack has already resolved; this provides no retroactive protection.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Your body falls prone and cannot act, move or take Reactions. It has 3 defense Banes. Your spirit appears in your square or an adjacent free square. The spirit has Speed 5, can speak, can pass through nonmagical solid objects and creatures, and is immune to mundane attacks. It cannot attack, cast spells, use equipment or physically interact with objects. Its movement does not provoke opportunity attacks. Magical attacks can target it; resolve them against your normal defenses, and damage to the spirit is damage to your body. If your body drops to 0 HP, the projection ends. At the end of your turn, choose Snap Back or Manifest.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Bruce replaced the escape Reaction with spirit projection.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Attribute also cleaned to None (no roll).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CHG-ODD-015</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>signature-odd-wrong-place-for-that</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Out of Body</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-wrong-place-for-that.md</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Immediate movement.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Until the end of your turn.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Projection lasts until turn end.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CHG-ODD-016</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>signature-odd-wrong-place-for-that</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Out of Body</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-wrong-place-for-that.md</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Skill / Utility / Movement</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Projection is utility and movement.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CHG-ODD-017</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>signature-odd-change-the-question</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A Door Where There Wasn’t</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-change-the-question.md</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Change the Question</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>A Door Where There Wasn’t</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>The ability is now a temporary passage.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHG-ODD-018</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>signature-odd-change-the-question</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A Door Where There Wasn’t</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-change-the-question.md</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>You stop pulling at the locked door and look up at the hinge, then show everyone the different problem you mean to solve.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>You knock politely on the wall, mutter an apology to the spirit, and a door opens where no door belongs.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Align the narrative with the impossible door.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CHG-ODD-019</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>signature-odd-change-the-question</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>A Door Where There Wasn’t</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-change-the-question.md</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Opening the passage is now a Maneuver.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CHG-ODD-020</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>signature-odd-change-the-question</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A Door Where There Wasn’t</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-change-the-question.md</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>One noncombat obstacle you and your companions can examine.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Self; one nonmagical barrier within reach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>The ability targets the Odd and a barrier.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CHG-ODD-021</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>signature-odd-change-the-question</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A Door Where There Wasn’t</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-change-the-question.md</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Spend one minute examining the obstacle and describe an alternative approach. The DA identifies one workable alternative using available people, tools or features, if one exists, and states its risks. If none exists, learn the concrete missing resource or access that prevents it. You and one ally each gain 1 Boon to the next roll pursuing that alternative this scene. This grants no automatic success or specialist permission.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>A door-sized opening appears in the barrier. Only you and your worn or carried gear can pass through it. The opening closes immediately after you pass through or at the end of your next turn.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Bruce replaced the alternative-approach analysis with a personal barrier passage.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Attribute also cleaned to None (no roll).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CHG-ODD-022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>signature-odd-change-the-question</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A Door Where There Wasn’t</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-change-the-question.md</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Information remains known; Boons expire when used or the scene ends.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Until you pass through or the end of your next turn.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>The opening is temporary.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CHG-ODD-023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>signature-odd-change-the-question</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A Door Where There Wasn’t</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-change-the-question.md</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>One examination of an obstacle per scene unless its circumstances change.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Once per scene; the barrier must be nonmagical and no more than one square thick.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>The passage is limited by scene and barrier type.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CHG-ODD-024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>signature-odd-change-the-question</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>A Door Where There Wasn’t</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-change-the-question.md</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Skill / Utility</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Skill / Utility / Movement</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>The ability now includes movement through a barrier.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CHG-ODD-025</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>signature-odd-always-a-way-around</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pocket Sand</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-always-a-way-around.md</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Always a Way Around</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Pocket Sand</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>The signature is now a dirty pocket trick, not a Force movement rider.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CHG-ODD-026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>signature-odd-always-a-way-around</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pocket Sand</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-always-a-way-around.md</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>You brace, tug or shove until something gives, then slip into the space the struggle has opened.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>You reach into a pocket that should not contain sand and throw it into exactly the wrong pair of eyes.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Align the narrative with the pocket trick.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CHG-ODD-027</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>signature-odd-always-a-way-around</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pocket Sand</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-always-a-way-around.md</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Reaction</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>The trick now reacts to an enemy roll.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CHG-ODD-028</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>signature-odd-always-a-way-around</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pocket Sand</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-always-a-way-around.md</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Self, after you resolve Force.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>That enemy.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>The target is the triggering enemy within 2.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CHG-ODD-029</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>signature-odd-always-a-way-around</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pocket Sand</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-always-a-way-around.md</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Move up to 2 squares without provoking after your Force action. If you reduced your own Grappled rating to 0, you may stand without spending movement before taking this move. The card does not let you use Force without a Main Action or move while still Grappled.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Throw grit or debris into its face. The target takes 1 Bane to that roll. After the roll resolves, it gains Blinded 1 until the end of its next turn.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Bruce replaced the Force rider with a Reaction that penalizes a roll and applies Blinded.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Attribute also cleaned to None (no roll).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CHG-ODD-030</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>signature-odd-always-a-way-around</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pocket Sand</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-always-a-way-around.md</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Immediate stand and movement if allowed.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>The triggering roll and the Blinded condition.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Match the new Reaction.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CHG-ODD-031</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>signature-odd-always-a-way-around</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pocket Sand</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-always-a-way-around.md</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Once on your turn.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>The dirty trick is limited to once per scene.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CHG-ODD-032</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>signature-odd-always-a-way-around</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pocket Sand</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-always-a-way-around.md</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Skill / Control</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>The trick now controls an enemy roll.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CHG-ODD-033</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>signature-odd-useful-interruption</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Use Their Voice</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-useful-interruption.md</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Useful Interruption</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Use Their Voice</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>The distraction is now the spirit’s borrowed voice.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CHG-ODD-034</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>signature-odd-useful-interruption</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Use Their Voice</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-useful-interruption.md</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>You point, stumble or call a name at exactly the wrong moment, giving your ally the half-second they need.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>You tilt your head toward a spirit only you can see. It calls out in the target’s own voice from an empty patch of air.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Align the narrative with the spirit.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CHG-ODD-035</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>signature-odd-useful-interruption</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Use Their Voice</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-useful-interruption.md</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>One creature within 3 squares that can see or hear your distraction; one willing ally within 3 squares.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>One enemy within 5 squares that can hear you; one willing ally within 5 squares that can see or hear you.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Range increases to 5 and the target is an enemy.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CHG-ODD-036</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>signature-odd-useful-interruption</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Use Their Voice</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-useful-interruption.md</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Describe a distraction the creature can perceive. The ally may move up to 2 squares without provoking from that creature. It also gains 1 Boon to its next roll against that creature before the start of your next turn. Other enemies can still react to the movement. This does not compel belief or grant Hidden.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>The spirit calls out in the target’s own voice from a point you choose within 5 squares. The target turns toward the voice. The ally may move up to 2 squares without provoking and gains 1 Boon to its next attack against that target before the start of your next turn.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Bruce replaced the generic distraction with the spirit’s borrowed voice.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Attribute also cleaned to None (no roll).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CHG-ODD-037</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>signature-odd-useful-interruption</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Use Their Voice</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-useful-interruption.md</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Immediate movement; Boon expires when used or at the start of your next turn.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Movement is immediate; the Boon expires when used or at the start of your next turn.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>No mechanical change.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CHG-ODD-038</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>signature-odd-useful-interruption</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Use Their Voice</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-useful-interruption.md</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Skill / Support</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Skill / Support / Control</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>The voice now also controls the target’s attention.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CHG-ODD-039</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>signature-odd-sideways-thinking</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Borrowed Tongue</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-sideways-thinking.md</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sideways Thinking</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Borrowed Tongue</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>The signature is now language possession, not a generic reasoning trick.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CHG-ODD-040</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>signature-odd-sideways-thinking</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Borrowed Tongue</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-sideways-thinking.md</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>You stop trying to solve the problem directly and approach it from an angle nobody else has considered.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>You go still for a moment, then answer in a language you have never learned. The spirit inside you remembers it for you.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Align the narrative with the possessing spirit.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CHG-ODD-041</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>signature-odd-sideways-thinking</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Borrowed Tongue</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-sideways-thinking.md</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Maneuver in combat, or one minute out of combat</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>The ability is now an active language possession.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CHG-ODD-042</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>signature-odd-sideways-thinking</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Borrowed Tongue</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-sideways-thinking.md</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Self, before an ordinary noncombat task roll.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Self; one language you hear spoken.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>The target is now a heard language.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHG-ODD-043</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>signature-odd-sideways-thinking</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Borrowed Tongue</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-sideways-thinking.md</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Describe a plausible approach based on reasoning. Use Reason for that roll and gain 1 Boon. You still need any specialist permission and suitable tools. This cannot replace an attribute printed on another learned card or make an impossible action possible.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>A spirit that knows the language possesses you. You understand and speak that language for the scene. You do not read or write it.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Bruce replaced the generic skill Boon with language possession.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Attribute also cleaned to None (no roll).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CHG-ODD-044</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>signature-odd-sideways-thinking</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Borrowed Tongue</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-sideways-thinking.md</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>The declared task.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Until the end of the scene.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>The language lasts for the scene.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CHG-ODD-045</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>signature-odd-sideways-thinking</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Borrowed Tongue</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-sideways-thinking.md</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Once per scene; you cannot use it on the same task again.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Once per scene; one language at a time.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Limit language switching.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CHG-ODD-046</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>signature-odd-sideways-thinking</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Borrowed Tongue</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-sideways-thinking.md</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Skill / Social</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Skill / Utility / Social</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>The ability now covers language utility.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CHG-ODD-047</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>signature-odd-strange-but-effective</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Borrowed Life</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-strange-but-effective.md</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Strange but Effective</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Borrowed Life</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>New title names the borrowed-expertise effect.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CHG-ODD-048</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>signature-odd-strange-but-effective</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Borrowed Life</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-strange-but-effective.md</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>You loop a strap, plant your heel against a unlikely purchase and pull with a grin as the whole problem lurches sideways.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>You open your mouth and a dead expert answers. For a few minutes, the greatest locksmith, duelist or scholar you have ever met is wearing your body.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Narrative now establishes the spirit-possession fantasy.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CHG-ODD-049</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>signature-odd-strange-but-effective</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Borrowed Life</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-strange-but-effective.md</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Main Action · Attribute: Guile</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Main Action · Attribute: None (no roll)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Removed the Guile roll; the effect now resolves automatically.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CHG-ODD-050</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>signature-odd-strange-but-effective</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Borrowed Life</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-strange-but-effective.md</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>One adjacent obstacle or creature, or your own Grappled condition.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Self.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Became self-only instead of targeting an obstacle, creature, or condition.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CHG-ODD-051</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>signature-odd-strange-but-effective</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Borrowed Life</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-strange-but-effective.md</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Choose Force’s intended result before rolling: obstacle progress, reducing your Grappled rating, or pushing a creature. Describe a plausible means of exerting force. - **Weak:** 2 progress, Grappled reduction, or squares of push. - **Standard:** 3 progress, Grappled reduction, or squares of push. - **Strong:** 4 progress, Grappled reduction, or squares of push. Afterward you may move up to 2 squares without provoking if able. Grappled 3 leaves no Main Action to spend; this cannot release a fully restrained user.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Once per scene, invite a spirit into your body. Choose one skill, tool or weapon. For the scene, you gain 3 Boons to rolls using that expertise. The spirit speaks through you and colors your mannerisms, but you remain in control.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Replaced the Force maneuver with a once-per-scene borrowed-expertise support effect.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CHG-ODD-052</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>signature-odd-strange-but-effective</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Borrowed Life</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-strange-but-effective.md</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Immediate progress, reduction or push, then movement.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Until the end of the scene.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Extended the benefit from the next turn to the scene.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CHG-ODD-053</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>signature-odd-strange-but-effective</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Borrowed Life</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-strange-but-effective.md</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Skill / Control / Utility</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Skill / Support / Utility</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Reclassified from Control to Support while retaining Utility.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CHG-ODD-054</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>signature-odd-strange-but-effective</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Borrowed Life</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-strange-but-effective.md</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Limited the effect to once per scene instead of repeatable use.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CHG-ODD-055</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>signature-odd-an-unexpected-exit</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>The Unseen Procession</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-an-unexpected-exit.md</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>An Unexpected Exit</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>The Unseen Procession</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>New title names the spectral witnesses and procession imagery.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CHG-ODD-056</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>signature-odd-an-unexpected-exit</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>The Unseen Procession</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-an-unexpected-exit.md</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>You spot the half-hidden stair, haul your companion toward it and disappear from the place everyone thought had you cornered.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>You call the dead of this place. They rise behind you, not to fight, but to be seen. The enemy line falters at the impossible crowd.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Narrative now establishes the spectral crowd.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CHG-ODD-057</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>signature-odd-an-unexpected-exit</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>The Unseen Procession</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-an-unexpected-exit.md</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Maneuver · Attribute: None — no roll</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Main Action · Attribute: None (no roll)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Changed from Maneuver to Main Action and removed the Guile roll.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CHG-ODD-058</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>signature-odd-an-unexpected-exit</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>The Unseen Procession</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-an-unexpected-exit.md</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Self and optionally one adjacent willing ally.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>You and each ally within 5 squares; each enemy within 5 squares.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Now affects every ally and enemy within 5 squares, not self plus one ally.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CHG-ODD-059</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>signature-odd-an-unexpected-exit</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>The Unseen Procession</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-an-unexpected-exit.md</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Move up to your Speed without provoking. The ally may follow along a legal route up to the same distance, spending no action, and must end in a separate free square adjacent to you. Both must be able to move; this does not cross standing occupied squares, barriers or otherwise impassable terrain.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Once per scene, spectral figures fill the area. You and each ally gain 1 Boon to your next defense and may move 1 square without provoking. Each enemy gains 1 Bane to its next attack.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Replaced the escape movement with area support and control.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CHG-ODD-060</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>signature-odd-an-unexpected-exit</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>The Unseen Procession</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-an-unexpected-exit.md</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Immediate movement.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Until the end of the round.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Changed from immediate movement to until the end of the round.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CHG-ODD-061</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>signature-odd-an-unexpected-exit</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>The Unseen Procession</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-an-unexpected-exit.md</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Skill / Support / Control</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Reclassified from Movement to Support and Control.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CHG-ODD-062</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>signature-odd-an-unexpected-exit</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>The Unseen Procession</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-an-unexpected-exit.md</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Once on your turn.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Changed once on your turn to once per scene.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CHG-ODD-063</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>signature-odd-one-last-remark</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Not Quite Yet</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-one-last-remark.md</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>One Last Remark</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Not Quite Yet</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>New title foregrounds the death-delay effect.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Reverted to Proposed: close-out recorded before decision. Approved 2026-10-27; delay moved to the beginning of the ally's next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CHG-ODD-064</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>signature-odd-one-last-remark</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Not Quite Yet</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-one-last-remark.md</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>You answer the cry of pain with a sharp, stubborn joke, giving your companion something to do before despair catches up.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>You catch the spirit at the threshold and hold up one finger. “Not quite yet.”</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Narrative now addresses the dying companion directly.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Reverted to Proposed: close-out recorded before decision. Approved 2026-10-27; delay moved to the beginning of the ally's next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CHG-ODD-065</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>signature-odd-one-last-remark</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Not Quite Yet</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-one-last-remark.md</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Reaction · Attribute: None — no roll</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Reaction · Attribute: None (no roll)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Standardized the Reaction metadata; no mechanical change.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Reverted to Proposed: close-out recorded before decision. Approved 2026-10-27; delay moved to the beginning of the ally's next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CHG-ODD-066</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>signature-odd-one-last-remark</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Not Quite Yet</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-one-last-remark.md</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>One willing ally within 4 squares that can hear you, after it takes damage; alternatively, when you hear an ally’s Last Words within 4 squares.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>One ally within 5 squares that would enter Last Words.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Increased range from 4 to 5 squares and limited the trigger to entering Last Words.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Reverted to Proposed: close-out recorded before decision. Approved 2026-10-27; delay moved to the beginning of the ally's next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CHG-ODD-067</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>signature-odd-one-last-remark</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Not Quite Yet</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-one-last-remark.md</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>After damage resolves, the chosen ally may move up to 3 squares without provoking or make one free Basic Melee attack against an adjacent enemy. It must be able to take the chosen action. If triggered by Last Words instead, choose up to two other willing allies within 4 squares that can hear you; each chooses one of those benefits. The dying speaker gains no action, and its death is neither delayed nor reversed. Basic Melee uses each attacker’s Brawn, weapon and normal outcomes. Damage from a free attack cannot trigger a free attack through this card; no further free attacks arise from these attacks.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>The ally does not enter Last Words yet. It remains at 0 HP with at least three death marks until the beginning of its next turn and makes no further death rolls during the delay. If it is stabilized or healed above 0 before then, it avoids Last Words. At the beginning of its next turn, if it still has three death marks, Last Words begin.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Replaced the free move or attack with a postponement of Last Words to the beginning of the ally's next turn.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Reverted to Proposed: close-out recorded before decision. Approved 2026-10-27; delay moved to the beginning of the ally's next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CHG-ODD-068</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>signature-odd-one-last-remark</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Not Quite Yet</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-one-last-remark.md</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Immediate chosen benefits.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Until the beginning of the ally’s next turn.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Changed from immediate benefits to the beginning of the ally's next turn.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Reverted to Proposed: close-out recorded before decision. Approved 2026-10-27; delay moved to the beginning of the ally's next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CHG-ODD-069</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>signature-odd-one-last-remark</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Not Quite Yet</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-one-last-remark.md</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Skill / Movement / Attack</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Skill / Support / Recovery</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Reclassified from Movement and Attack to Support and Recovery.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Reverted to Proposed: close-out recorded before decision. Approved 2026-10-27; delay moved to the beginning of the ally's next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CHG-ODD-070</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>signature-odd-one-last-remark</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Not Quite Yet</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-one-last-remark.md</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Normal Reaction cost; the Last Words benefit can trigger once per dying ally.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Once per day per character; uses your Reaction.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Changed from a per-dying-ally trigger to once per day per character.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Stable ID retained. Reverted to Proposed: close-out recorded before decision. Approved 2026-10-27; delay moved to the beginning of the ally's next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CHG-ODD-071</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CLS-05</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>signature-odd-unlikely-assistant</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Foul Wind</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>design/cards/signature-odd-unlikely-assistant.md</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Each willing ally within 5 squares may immediately fall prone. Make one Fortitude roll. Each non-prone creature within 5 squares other than you takes 1 poison damage on a Weak result, 2 poison damage on a Standard result, or 4 poison damage on a Strong result.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Each willing ally within 5 squares may immediately fall prone. Make one Fortitude roll. Each non-prone creature within 5 squares other than you takes poison damage: Weak: 1; Standard: 2; Strong: 4.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Clarity</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Made the three roll outcomes explicit for the card audit; no mechanical change.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>#1293</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Formatting-only follow-up to the approved level-3 card.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q204"/>
